--- a/tabla_restricciones_consolidado.xlsx
+++ b/tabla_restricciones_consolidado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fer\IA\01 Optimización de cargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A8F679-FFA1-419A-8073-BC3006B59CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B387F4AC-6461-4C59-864F-5F54308CDBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>DUNS Proveedor</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>Upsilon Metalurgia Sul</t>
+  </si>
+  <si>
+    <t>Grupo de consolidación</t>
   </si>
 </sst>
 </file>
@@ -511,15 +514,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="3" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -529,8 +532,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>111000001</v>
       </c>
@@ -538,8 +544,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>222000002</v>
       </c>
@@ -549,8 +558,11 @@
       <c r="C3" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>333000003</v>
       </c>
@@ -560,8 +572,11 @@
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>444000004</v>
       </c>
@@ -571,17 +586,25 @@
       <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>555000005</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>112000011</v>
       </c>
@@ -591,8 +614,11 @@
       <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>223000012</v>
       </c>
@@ -602,8 +628,11 @@
       <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>334000013</v>
       </c>
@@ -611,8 +640,11 @@
         <v>15</v>
       </c>
       <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>666000006</v>
       </c>
@@ -620,8 +652,11 @@
         <v>16</v>
       </c>
       <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>777000007</v>
       </c>
@@ -631,8 +666,11 @@
       <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>888000008</v>
       </c>
@@ -642,19 +680,23 @@
       <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>999000009</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>101000010</v>
       </c>
@@ -662,8 +704,11 @@
         <v>22</v>
       </c>
       <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>445000014</v>
       </c>
@@ -673,8 +718,11 @@
       <c r="C15" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>556000015</v>
       </c>
@@ -684,8 +732,11 @@
       <c r="C16" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>667000016</v>
       </c>
@@ -693,8 +744,11 @@
         <v>27</v>
       </c>
       <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>778000017</v>
       </c>
@@ -702,8 +756,11 @@
         <v>28</v>
       </c>
       <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>889000018</v>
       </c>
@@ -713,8 +770,11 @@
       <c r="C19" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>990000019</v>
       </c>
@@ -724,8 +784,11 @@
       <c r="C20" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>100100020</v>
       </c>
@@ -734,6 +797,9 @@
       </c>
       <c r="C21" s="5" t="s">
         <v>32</v>
+      </c>
+      <c r="D21" s="5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
